--- a/public/templates/champion-import-template.xlsx
+++ b/public/templates/champion-import-template.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Інструкція" sheetId="1" r:id="R5ff95ee083d14f59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Гравці" sheetId="2" r:id="Rf1716ffd0f1749dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Фізичні тести" sheetId="3" r:id="Ra61b8c72ace447dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ігрова діяльність" sheetId="4" r:id="Rbd49db2d85314459"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Навчальні завдання" sheetId="5" r:id="Rb56f24229d7e4afd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Термінологія" sheetId="6" r:id="R606289a6cca24bca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Налаштування показників" sheetId="7" r:id="Rf7051c88d12f4b2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Умови тестування" sheetId="8" r:id="Rdf8e845987d8446a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Інструкція" sheetId="1" r:id="R624df7e385fb46fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Гравці" sheetId="2" r:id="Rde207c0546784ed9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Фізичні тести" sheetId="3" r:id="R33c78baaa7f1418e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ігрова діяльність" sheetId="4" r:id="R9dfec07300e7446f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Навчальні завдання" sheetId="5" r:id="R49f5b62b41374859"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Термінологія" sheetId="6" r:id="Reced8c4cb1d342cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Налаштування показників" sheetId="7" r:id="R9bc9f43bf9a34da0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Умови тестування" sheetId="8" r:id="Rc5012e4643904174"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1031,7 +1031,7 @@
         <x:v>Фізичні тести</x:v>
       </x:c>
       <x:c r="B20" s="61" t="str">
-        <x:v>4 тести / 5 полів для U6–U12; 4 тести / 6 полів для U13–U15</x:v>
+        <x:v>4 тести / 5 полів для U6–U12; 4 тести / 6 полів для U13–U17</x:v>
       </x:c>
       <x:c r="C20" s="61" t="str">
         <x:v>Тест 505 має правий і лівий результати; стрибок — лише кращу спробу</x:v>
@@ -1781,7 +1781,7 @@
     <x:row r="3"/>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="45" t="str">
-        <x:v>11 прикладів: 4 тести й 5 полів для U6–U12; 4 тести й 6 полів для U13–U15. Додавайте власні записи з рядка 18; приклади не імпортуються.</x:v>
+        <x:v>11 прикладів: 4 тести й 5 полів для U6–U12; 4 тести й 6 полів для U13–U17. Додавайте власні записи з рядка 18; приклади не імпортуються.</x:v>
       </x:c>
       <x:c r="B4" s="45"/>
       <x:c r="C4" s="45"/>
@@ -1931,7 +1931,7 @@
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="122" t="str">
-        <x:v>ПРИКЛАД — U14A</x:v>
+        <x:v>ПРИКЛАД — U16A</x:v>
       </x:c>
       <x:c r="B12" s="122" t="str">
         <x:v>Шевченко Максим Ігорович</x:v>
@@ -1954,7 +1954,7 @@
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="122" t="str">
-        <x:v>ПРИКЛАД — U14A</x:v>
+        <x:v>ПРИКЛАД — U16A</x:v>
       </x:c>
       <x:c r="B13" s="122" t="str">
         <x:v>Шевченко Максим Ігорович</x:v>
@@ -1977,7 +1977,7 @@
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="122" t="str">
-        <x:v>ПРИКЛАД — U14A</x:v>
+        <x:v>ПРИКЛАД — U16A</x:v>
       </x:c>
       <x:c r="B14" s="122" t="str">
         <x:v>Шевченко Максим Ігорович</x:v>
@@ -2000,7 +2000,7 @@
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="122" t="str">
-        <x:v>ПРИКЛАД — U14A</x:v>
+        <x:v>ПРИКЛАД — U16A</x:v>
       </x:c>
       <x:c r="B15" s="122" t="str">
         <x:v>Шевченко Максим Ігорович</x:v>
@@ -2023,7 +2023,7 @@
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="122" t="str">
-        <x:v>ПРИКЛАД — U14A</x:v>
+        <x:v>ПРИКЛАД — U16A</x:v>
       </x:c>
       <x:c r="B16" s="122" t="str">
         <x:v>Шевченко Максим Ігорович</x:v>
@@ -2046,7 +2046,7 @@
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="122" t="str">
-        <x:v>ПРИКЛАД — U14A</x:v>
+        <x:v>ПРИКЛАД — U16A</x:v>
       </x:c>
       <x:c r="B17" s="122" t="str">
         <x:v>Шевченко Максим Ігорович</x:v>
@@ -5572,7 +5572,7 @@
         <x:v>Фізичний тест</x:v>
       </x:c>
       <x:c r="B11" s="127" t="str">
-        <x:v>U13–U15</x:v>
+        <x:v>U13–U17</x:v>
       </x:c>
       <x:c r="C11" s="127" t="n">
         <x:v>1</x:v>
@@ -5595,7 +5595,7 @@
         <x:v>Фізичний тест</x:v>
       </x:c>
       <x:c r="B12" s="127" t="str">
-        <x:v>U13–U15</x:v>
+        <x:v>U13–U17</x:v>
       </x:c>
       <x:c r="C12" s="127" t="n">
         <x:v>2</x:v>
@@ -5618,7 +5618,7 @@
         <x:v>Фізичний тест</x:v>
       </x:c>
       <x:c r="B13" s="127" t="str">
-        <x:v>U13–U15</x:v>
+        <x:v>U13–U17</x:v>
       </x:c>
       <x:c r="C13" s="127" t="n">
         <x:v>2</x:v>
@@ -5641,7 +5641,7 @@
         <x:v>Фізичний тест</x:v>
       </x:c>
       <x:c r="B14" s="127" t="str">
-        <x:v>U13–U15</x:v>
+        <x:v>U13–U17</x:v>
       </x:c>
       <x:c r="C14" s="127" t="n">
         <x:v>3</x:v>
@@ -5664,7 +5664,7 @@
         <x:v>Фізичний тест</x:v>
       </x:c>
       <x:c r="B15" s="127" t="str">
-        <x:v>U13–U15</x:v>
+        <x:v>U13–U17</x:v>
       </x:c>
       <x:c r="C15" s="127" t="n">
         <x:v>3</x:v>
@@ -5687,7 +5687,7 @@
         <x:v>Фізичний тест</x:v>
       </x:c>
       <x:c r="B16" s="127" t="str">
-        <x:v>U13–U15</x:v>
+        <x:v>U13–U17</x:v>
       </x:c>
       <x:c r="C16" s="127" t="n">
         <x:v>4</x:v>
